--- a/data/trans_orig/P21D_2_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203060</t>
+          <t>203081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130006</t>
+          <t>129609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140174</t>
+          <t>140171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333895</t>
+          <t>333818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>343891</t>
+          <t>343922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>196018</t>
+          <t>196831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279106</t>
+          <t>278929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288458</t>
+          <t>288652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>480930</t>
+          <t>480971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492320</t>
+          <t>492411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206922</t>
+          <t>207147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214672</t>
+          <t>214487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246439</t>
+          <t>245879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254954</t>
+          <t>254576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>457335</t>
+          <t>457463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>467782</t>
+          <t>468240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38609</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505317</t>
+          <t>506169</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524651</t>
+          <t>524930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285885</t>
+          <t>287626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316952</t>
+          <t>317230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>808810</t>
+          <t>809179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>840844</t>
+          <t>840881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221216</t>
+          <t>222524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233443</t>
+          <t>233604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212824</t>
+          <t>212770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>221837</t>
+          <t>221815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>438015</t>
+          <t>438474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>453124</t>
+          <t>452752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149731</t>
+          <t>151134</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180788</t>
+          <t>180469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185284</t>
+          <t>185285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>334010</t>
+          <t>334047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340687</t>
+          <t>340742</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>557</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>165741</t>
+          <t>165753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170050</t>
+          <t>170056</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>284172</t>
+          <t>283477</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288270</t>
+          <t>288265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1626144</t>
+          <t>1626254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1648715</t>
+          <t>1649240</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1535192</t>
+          <t>1532753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1566211</t>
+          <t>1565875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3173584</t>
+          <t>3171629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3210829</t>
+          <t>3211476</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_2_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>203778</t>
+          <t>208466</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203081</t>
+          <t>198970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>137351</t>
+          <t>157521</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129609</t>
+          <t>148197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140171</t>
+          <t>161778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>341128</t>
+          <t>365987</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333818</t>
+          <t>354316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>343922</t>
+          <t>371455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203013</t>
+          <t>224417</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>196831</t>
+          <t>217477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>285747</t>
+          <t>243050</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278929</t>
+          <t>236983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288652</t>
+          <t>246544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>488760</t>
+          <t>467466</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>480971</t>
+          <t>459737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492411</t>
+          <t>471887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>248680</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>248680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>248680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>494181</t>
+          <t>475492</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>494181</t>
+          <t>475492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>494181</t>
+          <t>475492</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>212425</t>
+          <t>245689</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207147</t>
+          <t>238780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214487</t>
+          <t>249826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>251514</t>
+          <t>289788</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245879</t>
+          <t>283924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254576</t>
+          <t>293137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>463939</t>
+          <t>535477</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>457463</t>
+          <t>527385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>468240</t>
+          <t>541120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>517529</t>
+          <t>306399</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506169</t>
+          <t>297937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524930</t>
+          <t>311699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>310545</t>
+          <t>339368</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287626</t>
+          <t>334293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317230</t>
+          <t>342558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>828073</t>
+          <t>645766</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>809179</t>
+          <t>636789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>840881</t>
+          <t>651985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>29535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>228737</t>
+          <t>247999</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222524</t>
+          <t>240831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>252653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>218225</t>
+          <t>242369</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212770</t>
+          <t>236340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>221815</t>
+          <t>246920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>446962</t>
+          <t>490368</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>438474</t>
+          <t>482122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>452752</t>
+          <t>497542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>154605</t>
+          <t>172202</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151134</t>
+          <t>168261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>183742</t>
+          <t>197265</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180469</t>
+          <t>193645</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185285</t>
+          <t>198889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>338346</t>
+          <t>369467</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>334047</t>
+          <t>364830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340742</t>
+          <t>371783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>168598</t>
+          <t>184696</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>165753</t>
+          <t>181603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170056</t>
+          <t>186188</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>286805</t>
+          <t>314257</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>283477</t>
+          <t>310988</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288265</t>
+          <t>315749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84305</t>
+          <t>91886</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1638291</t>
+          <t>1534733</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1626254</t>
+          <t>1520127</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1649240</t>
+          <t>1544082</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1555723</t>
+          <t>1654056</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1532753</t>
+          <t>1640459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1565875</t>
+          <t>1663970</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3194013</t>
+          <t>3188789</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3171629</t>
+          <t>3170999</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3211476</t>
+          <t>3202434</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
